--- a/VerveStacks_NGA_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_NGA_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8A75123-C883-4DEC-934C-837D6B7ECBBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6529E929-98EF-489E-9F28-369B29C76E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7205F60D-C243-4775-8B15-D0470A4CAC66}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6F22813E-D502-4A0B-BCF2-27656287D987}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1018,7 +1018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D832E066-4D85-4A20-9A66-C743DC1482F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C70C01E2-B091-40AE-97A4-0341EBE7171C}">
   <dimension ref="B3:L73"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NGA_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_NGA_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6529E929-98EF-489E-9F28-369B29C76E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA6EF3AB-F485-404F-A19E-EFC0E0621422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6F22813E-D502-4A0B-BCF2-27656287D987}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{60A91833-0A44-4925-A325-107EBE9E2190}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1018,7 +1018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C70C01E2-B091-40AE-97A4-0341EBE7171C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41482D60-AC8D-491B-A593-8725E43B161B}">
   <dimension ref="B3:L73"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NGA_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_NGA_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA6EF3AB-F485-404F-A19E-EFC0E0621422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4303D7C9-8DC8-4BC0-8082-F9E9EC137F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{60A91833-0A44-4925-A325-107EBE9E2190}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4FD74A8B-38DB-4F76-AA34-DDAEA5BDF98E}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1018,7 +1018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41482D60-AC8D-491B-A593-8725E43B161B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2BA4BF3-B275-4573-A207-5917961097D7}">
   <dimension ref="B3:L73"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NGA_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_NGA_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4303D7C9-8DC8-4BC0-8082-F9E9EC137F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8557FED1-E0BD-4817-81FD-2AAE35D4DFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4FD74A8B-38DB-4F76-AA34-DDAEA5BDF98E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EB196238-7619-4DFC-B6AE-6E026A94DCBB}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1018,7 +1018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2BA4BF3-B275-4573-A207-5917961097D7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C63E3EC1-FEB0-4205-998A-3AA8C46137A6}">
   <dimension ref="B3:L73"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NGA_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_NGA_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8557FED1-E0BD-4817-81FD-2AAE35D4DFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{83C31256-0FED-4F84-BD67-C60192ABF95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EB196238-7619-4DFC-B6AE-6E026A94DCBB}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4C921687-0AE4-45FC-ACF6-F585B07C4176}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1018,7 +1018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C63E3EC1-FEB0-4205-998A-3AA8C46137A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E833FD3D-441E-4BF6-B501-829D4A7CE904}">
   <dimension ref="B3:L73"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NGA_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_NGA_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83C31256-0FED-4F84-BD67-C60192ABF95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{40C3E484-D85C-4B42-9C46-73C8D040F35E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4C921687-0AE4-45FC-ACF6-F585B07C4176}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DE53BB4B-CB39-43AB-9DD4-9DD68FD3F985}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1018,7 +1018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E833FD3D-441E-4BF6-B501-829D4A7CE904}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F03871AA-B7A4-4B28-A098-3E3D450FE1D0}">
   <dimension ref="B3:L73"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
